--- a/research/runs/20260302-070309-excel-formula-language-pass2-pack-01/fixtures/formula_parse_pass2/FMLP2-021.xlsx
+++ b/research/runs/20260302-070309-excel-formula-language-pass2-pack-01/fixtures/formula_parse_pass2/FMLP2-021.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\DnaCalc\Foundation\research\runs\20260302-070309-excel-formula-language-pass2-pack-01\fixtures\formula_parse_pass2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96666ADA-0597-44F6-BD29-8141D84A63B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006862DC-AF05-4AFE-9EC0-CDF1FB6BA5F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3135" yWindow="3885" windowWidth="11955" windowHeight="11595" xr2:uid="{39E4F4CD-3BBE-4B61-9ACA-C391009BF7ED}"/>
+    <workbookView xWindow="3135" yWindow="3885" windowWidth="11955" windowHeight="11595" xr2:uid="{B691D642-1419-4F74-B81A-F0A0CE72A0E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -91,11 +91,20 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="A1">
+            <v>77</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -417,7 +426,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02A05133-F548-46AF-ABFB-044ABFF52BA1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFE7ADFC-F6F4-4D34-B165-9CFE7A12F1EB}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -431,9 +440,9 @@
       <c r="C1">
         <v>7</v>
       </c>
-      <c r="D1" t="e">
+      <c r="D1">
         <f>[1]Sheet1!A1</f>
-        <v>#REF!</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">

--- a/research/runs/20260302-070309-excel-formula-language-pass2-pack-01/fixtures/formula_parse_pass2/FMLP2-021.xlsx
+++ b/research/runs/20260302-070309-excel-formula-language-pass2-pack-01/fixtures/formula_parse_pass2/FMLP2-021.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\DnaCalc\Foundation\research\runs\20260302-070309-excel-formula-language-pass2-pack-01\fixtures\formula_parse_pass2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006862DC-AF05-4AFE-9EC0-CDF1FB6BA5F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9EDE1D6-9053-452D-A121-B1FE8A99C32F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3135" yWindow="3885" windowWidth="11955" windowHeight="11595" xr2:uid="{B691D642-1419-4F74-B81A-F0A0CE72A0E3}"/>
   </bookViews>
